--- a/data/fmsForecastOutput/File1/RPT_RPT1980057586629RA_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT1980057586629RA_fmsForecastOutput.xlsx
@@ -1878,13 +1878,13 @@
         <v>424.9978955549008</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>459.3471523764514</v>
+        <v>459.3471523764515</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>497.6939874785634</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>532.828965338997</v>
+        <v>532.8289653389973</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>576.5774865099629</v>
@@ -1893,28 +1893,28 @@
         <v>43.81590767946712</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>49.39988838981795</v>
+        <v>49.39988838981796</v>
       </c>
       <c r="J8" s="149" t="n">
         <v>55.86605061778214</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>62.97551947378584</v>
+        <v>62.97551947378587</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>72.22768689234547</v>
+        <v>72.22768689234549</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>54105255.78110533</v>
+        <v>54105255.78110534</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>61968274.46295174</v>
+        <v>61968274.46295175</v>
       </c>
       <c r="O8" s="152" t="n">
         <v>71069747.56810726</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>81151174.32249099</v>
+        <v>81151174.32249103</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>94568159.07589416</v>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>516.7822217612953</v>
+        <v>516.7822217612954</v>
       </c>
       <c r="U8" s="149" t="n">
         <v>558.5496880046601</v>
@@ -1934,37 +1934,37 @@
         <v>605.1780662833556</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>647.9009411732227</v>
+        <v>647.900941173223</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>701.0975762765186</v>
+        <v>701.0975762765187</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>54.2512545884915</v>
+        <v>54.25125458849151</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>61.15959929940809</v>
+        <v>61.1595992994081</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>69.15841598668581</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>77.95003581844497</v>
+        <v>77.95003581844502</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>89.38933646815633</v>
+        <v>89.38933646815634</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>54105255.78110533</v>
+        <v>54105255.78110534</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>61968274.46295174</v>
+        <v>61968274.46295175</v>
       </c>
       <c r="AF8" s="152" t="n">
         <v>71069747.56810726</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>81151174.32249099</v>
+        <v>81151174.32249103</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>94568159.07589416</v>
@@ -2061,7 +2061,7 @@
         <v>33381515.4286784</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>37598302.51098074</v>
+        <v>37598302.51098073</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>43242042.11055609</v>
@@ -2090,7 +2090,7 @@
         <v>101.0285123397635</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>110.036028509595</v>
+        <v>110.0360285095949</v>
       </c>
       <c r="AA9" s="156" t="n">
         <v>122.5552382034352</v>
@@ -2111,7 +2111,7 @@
         <v>33381515.4286784</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>37598302.51098074</v>
+        <v>37598302.51098073</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>43242042.11055609</v>
@@ -2179,10 +2179,10 @@
         <v>643.1735596663563</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>685.6187301607029</v>
+        <v>685.6187301607031</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>738.6845892867384</v>
+        <v>738.6845892867386</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>54.00176175699448</v>
@@ -2194,10 +2194,10 @@
         <v>67.57736704182565</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>75.94266948672937</v>
+        <v>75.9426694867294</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>86.86139061470848</v>
+        <v>86.8613906147085</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>81254741.23256612</v>
@@ -2209,10 +2209,10 @@
         <v>104451262.9967857</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>118749476.8334717</v>
+        <v>118749476.8334718</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>137810201.1864502</v>
+        <v>137810201.1864503</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2223,31 +2223,31 @@
         <v>660.9543181563653</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>708.2699798521671</v>
+        <v>708.2699798521672</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>763.6531134149484</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>814.0559147256938</v>
+        <v>814.0559147256942</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>877.0303824483391</v>
+        <v>877.0303824483393</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>64.18024422061214</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>71.46201658102878</v>
+        <v>71.46201658102879</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>80.3461148322091</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>90.30536722908363</v>
+        <v>90.30536722908366</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>103.3051404224296</v>
+        <v>103.3051404224297</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>81254741.23256612</v>
@@ -2259,10 +2259,10 @@
         <v>104451262.9967857</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>118749476.8334717</v>
+        <v>118749476.8334718</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>137810201.1864502</v>
+        <v>137810201.1864503</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2324,7 +2324,7 @@
         <v>1587.196473349733</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1725.329084324414</v>
+        <v>1725.329084324413</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>1851.39275677744</v>
@@ -2351,7 +2351,7 @@
         <v>10376046.68896653</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>11743099.19389895</v>
+        <v>11743099.19389896</v>
       </c>
       <c r="O11" s="159" t="n">
         <v>13456684.86246902</v>
@@ -2389,7 +2389,7 @@
         <v>206.8212572008018</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>234.0312203576259</v>
+        <v>234.0312203576258</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>264.9139632335063</v>
@@ -2401,7 +2401,7 @@
         <v>10376046.68896653</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>11743099.19389895</v>
+        <v>11743099.19389896</v>
       </c>
       <c r="AF11" s="159" t="n">
         <v>13456684.86246902</v>
@@ -2464,16 +2464,16 @@
         <v>599.499837723778</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>642.2169656491465</v>
+        <v>642.2169656491466</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>692.7640104987242</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>739.0794543267654</v>
+        <v>739.0794543267655</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>796.7460324023087</v>
+        <v>796.7460324023089</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>58.39684634774519</v>
@@ -2485,10 +2485,10 @@
         <v>73.1499482663223</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>82.27103912789823</v>
+        <v>82.27103912789825</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>94.13649571300641</v>
+        <v>94.13649571300644</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>91630787.92153265</v>
@@ -2500,7 +2500,7 @@
         <v>117907947.8592547</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>134161345.4498633</v>
+        <v>134161345.4498634</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>155762140.7638843</v>
@@ -2514,28 +2514,28 @@
         <v>714.134438307596</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>765.609388260513</v>
+        <v>765.6093882605131</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>826.144630217074</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>881.3871912673445</v>
+        <v>881.3871912673447</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>950.1103235131866</v>
+        <v>950.1103235131868</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>69.30897471153564</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>77.19487889677951</v>
+        <v>77.19487889677953</v>
       </c>
       <c r="AA12" s="162" t="n">
         <v>86.85566751168012</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>97.70306991960491</v>
+        <v>97.70306991960493</v>
       </c>
       <c r="AC12" s="163" t="n">
         <v>111.8153894187737</v>
@@ -2550,7 +2550,7 @@
         <v>117907947.8592547</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>134161345.4498633</v>
+        <v>134161345.4498634</v>
       </c>
       <c r="AH12" s="166" t="n">
         <v>155762140.7638843</v>
@@ -2603,46 +2603,46 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>1600.346021993753</v>
+        <v>1600.346021993752</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>1563.747862346919</v>
+        <v>1563.747862346918</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>1621.319610285061</v>
+        <v>1621.31961028506</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>1658.83533257231</v>
+        <v>1658.835332572309</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>1722.970589399678</v>
+        <v>1722.970589399677</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>1531.873884588692</v>
+        <v>1531.873884588691</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>1484.226340109034</v>
+        <v>1484.226340109033</v>
       </c>
       <c r="J13" s="156" t="n">
         <v>1531.18784064478</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>1573.312500371145</v>
+        <v>1573.312500371144</v>
       </c>
       <c r="L13" s="157" t="n">
         <v>1640.497096024352</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.86328735</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>9094600.965851342</v>
+        <v>9094600.965851337</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>10671201.6267484</v>
+        <v>10671201.62674839</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>12494903.11074286</v>
+        <v>12494903.11074285</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>14909967.45920723</v>
@@ -2656,43 +2656,43 @@
         <v>1307.941244282315</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>1278.03006144494</v>
+        <v>1278.030061444939</v>
       </c>
       <c r="V13" s="156" t="n">
         <v>1325.082675441448</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>1355.743769863644</v>
+        <v>1355.743769863642</v>
       </c>
       <c r="X13" s="157" t="n">
         <v>1408.160651253236</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>1243.282040052269</v>
+        <v>1243.282040052268</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>1203.03500481987</v>
+        <v>1203.035004819869</v>
       </c>
       <c r="AA13" s="156" t="n">
         <v>1240.146584247042</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>1275.098196191383</v>
+        <v>1275.098196191382</v>
       </c>
       <c r="AC13" s="157" t="n">
         <v>1330.343972035406</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.86328735</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>9094600.965851342</v>
+        <v>9094600.965851337</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>10671201.6267484</v>
+        <v>10671201.62674839</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>12494903.11074286</v>
+        <v>12494903.11074285</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>14909967.45920723</v>
@@ -2749,13 +2749,13 @@
         <v>632.3682303313176</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>674.3179237214455</v>
+        <v>674.3179237214456</v>
       </c>
       <c r="E14" s="168" t="n">
         <v>727.3353954211973</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>775.7239559723679</v>
+        <v>775.723955972368</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>836.0071408301949</v>
@@ -2770,7 +2770,7 @@
         <v>79.42693043891836</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>89.49736055841201</v>
+        <v>89.49736055841203</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>102.5840140052723</v>
@@ -2799,13 +2799,13 @@
         <v>742.1368818873068</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>791.2366428989874</v>
+        <v>791.2366428989875</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>852.7942290062317</v>
+        <v>852.7942290062319</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>908.4684907969927</v>
+        <v>908.4684907969929</v>
       </c>
       <c r="X14" s="169" t="n">
         <v>977.8990839965312</v>
@@ -2814,13 +2814,13 @@
         <v>75.21135024977916</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>83.50788269525447</v>
+        <v>83.50788269525448</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>94.11990632818184</v>
+        <v>94.11990632818186</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>106.0457208449082</v>
+        <v>106.0457208449083</v>
       </c>
       <c r="AC14" s="169" t="n">
         <v>121.5408015229583</v>
@@ -3846,7 +3846,7 @@
         <v>5815.89985498167</v>
       </c>
       <c r="E24" s="80" t="n">
-        <v>6581.800133085534</v>
+        <v>6581.800133085533</v>
       </c>
       <c r="F24" s="80" t="n">
         <v>7532.334804665247</v>
@@ -3896,7 +3896,7 @@
         <v>7116.108799169399</v>
       </c>
       <c r="V24" s="80" t="n">
-        <v>8053.234582659765</v>
+        <v>8053.234582659764</v>
       </c>
       <c r="W24" s="80" t="n">
         <v>9216.271826939363</v>
@@ -3926,7 +3926,7 @@
         <v>7559.714330351571</v>
       </c>
       <c r="AF24" s="80" t="n">
-        <v>8604.790564518178</v>
+        <v>8604.790564518176</v>
       </c>
       <c r="AG24" s="80" t="n">
         <v>9799.169309519959</v>
@@ -4019,7 +4019,7 @@
         <v>1221520.607621158</v>
       </c>
       <c r="AC25" s="93" t="n">
-        <v>1229707.778647045</v>
+        <v>1229707.778647044</v>
       </c>
       <c r="AD25" s="91" t="n">
         <v>1328742.888579021</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>436.9820758243247</v>
+        <v>436.9820758243248</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>483.4074092939737</v>
@@ -4417,37 +4417,37 @@
         <v>527.1048671951828</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>571.4757957694042</v>
+        <v>571.4757957694044</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>619.9530179160433</v>
+        <v>619.9530179160434</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>45.05143788277217</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>51.98741723419373</v>
+        <v>51.98741723419374</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>59.16741598746712</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>67.54322202130362</v>
+        <v>67.54322202130365</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>77.66132655828366</v>
+        <v>77.66132655828368</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>55630927.19168363</v>
+        <v>55630927.19168364</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>65214125.87750943</v>
+        <v>65214125.87750944</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>75269564.82490331</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>87037182.54892887</v>
+        <v>87037182.54892892</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>101682457.2404667</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>531.3545558137607</v>
+        <v>531.3545558137608</v>
       </c>
       <c r="U35" s="149" t="n">
         <v>587.8060988152366</v>
@@ -4467,37 +4467,37 @@
         <v>640.9406428110913</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>694.8941030282508</v>
+        <v>694.8941030282512</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>753.8406691825292</v>
+        <v>753.8406691825293</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>55.78104290422424</v>
+        <v>55.78104290422425</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>64.36309291965483</v>
+        <v>64.36309291965485</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>73.24528443426564</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>83.6038609899106</v>
+        <v>83.60386098991064</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>96.11403533701549</v>
+        <v>96.11403533701551</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>55630927.19168363</v>
+        <v>55630927.19168364</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>65214125.87750943</v>
+        <v>65214125.87750944</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>75269564.82490331</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>87037182.54892887</v>
+        <v>87037182.54892892</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>101682457.2404667</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>1510.766467326617</v>
+        <v>1510.766467326618</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>1663.983238904999</v>
@@ -4534,7 +4534,7 @@
         <v>129.3077747656707</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>146.659439473674</v>
+        <v>146.6594394736739</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>167.7653079741257</v>
@@ -4543,13 +4543,13 @@
         <v>27924493.02874498</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>31347726.67879767</v>
+        <v>31347726.67879766</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>35366836.91239465</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>40339861.37275728</v>
+        <v>40339861.37275727</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>46512395.4456106</v>
@@ -4563,13 +4563,13 @@
         <v>1531.027542089219</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1686.299122621183</v>
+        <v>1686.299122621182</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1828.46895604642</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1956.211898292792</v>
+        <v>1956.211898292791</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>2090.737679177501</v>
@@ -4593,13 +4593,13 @@
         <v>27924493.02874498</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>31347726.67879767</v>
+        <v>31347726.67879766</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>35366836.91239465</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>40339861.37275728</v>
+        <v>40339861.37275727</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>46512395.4456106</v>
@@ -4615,43 +4615,43 @@
         <v>573.1187088488806</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>628.0687941264349</v>
+        <v>628.068794126435</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>681.2594342324493</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>735.4313419644</v>
+        <v>735.4313419644002</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>794.3479724169136</v>
+        <v>794.3479724169138</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>55.53078906909032</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>63.27150675957718</v>
+        <v>63.27150675957719</v>
       </c>
       <c r="J37" s="162" t="n">
         <v>71.57899783957942</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>81.46017148611648</v>
+        <v>81.46017148611651</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>93.40680788092614</v>
+        <v>93.40680788092615</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>83555420.22042862</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>96561852.55630709</v>
+        <v>96561852.55630711</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>110636401.737298</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>127377043.9216861</v>
+        <v>127377043.9216862</v>
       </c>
       <c r="Q37" s="166" t="n">
         <v>148194852.6860773</v>
@@ -4665,28 +4665,28 @@
         <v>679.6688410094621</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>745.4520700661197</v>
+        <v>745.4520700661199</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>808.8732507362269</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>873.1999396522441</v>
+        <v>873.1999396522444</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>943.1187764706975</v>
+        <v>943.1187764706978</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>65.9974691243457</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>75.21356221048124</v>
+        <v>75.21356221048126</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>85.10385402310463</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>96.86636972753968</v>
+        <v>96.86636972753971</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>111.089672134676</v>
@@ -4695,13 +4695,13 @@
         <v>83555420.22042862</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>96561852.55630709</v>
+        <v>96561852.55630711</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>110636401.737298</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>127377043.9216861</v>
+        <v>127377043.9216862</v>
       </c>
       <c r="AH37" s="166" t="n">
         <v>148194852.6860773</v>
@@ -4717,7 +4717,7 @@
         <v>1512.637896735635</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1670.731251892079</v>
+        <v>1670.73125189208</v>
       </c>
       <c r="E38" s="156" t="n">
         <v>1827.748372003226</v>
@@ -4732,10 +4732,10 @@
         <v>165.6055834336825</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>189.1797478488411</v>
+        <v>189.1797478488412</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>215.3011134836874</v>
+        <v>215.3011134836873</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>246.5867919545623</v>
@@ -4770,7 +4770,7 @@
         <v>2192.898885774599</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>2398.989881767719</v>
+        <v>2398.989881767718</v>
       </c>
       <c r="W38" s="156" t="n">
         <v>2606.942697397957</v>
@@ -4785,7 +4785,7 @@
         <v>217.7063418190006</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>247.9238227031181</v>
+        <v>247.923822703118</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>284.2011063812637</v>
@@ -4819,16 +4819,16 @@
         <v>616.482457754597</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>675.9411837887241</v>
+        <v>675.9411837887242</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>733.7980037844927</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>792.7890633145138</v>
+        <v>792.7890633145139</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>856.7996496207121</v>
+        <v>856.7996496207123</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>60.05111110332436</v>
@@ -4840,10 +4840,10 @@
         <v>77.4827866362799</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>88.24975402344386</v>
+        <v>88.24975402344387</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>101.2319023418733</v>
+        <v>101.2319023418734</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>94226503.14358237</v>
@@ -4855,7 +4855,7 @@
         <v>124891904.6865043</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>143910978.4063716</v>
+        <v>143910978.4063717</v>
       </c>
       <c r="Q39" s="166" t="n">
         <v>167502494.1489516</v>
@@ -4869,22 +4869,22 @@
         <v>734.364425129191</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>805.8132125137512</v>
+        <v>805.8132125137513</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>875.0790619942045</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>945.4384392524483</v>
+        <v>945.4384392524486</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>1021.723559554635</v>
+        <v>1021.723559554636</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>71.2723580324065</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>81.24855090237945</v>
+        <v>81.24855090237946</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>92.00032691010856</v>
@@ -4905,7 +4905,7 @@
         <v>124891904.6865043</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>143910978.4063716</v>
+        <v>143910978.4063717</v>
       </c>
       <c r="AH39" s="166" t="n">
         <v>167502494.1489516</v>
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>1646.107819372303</v>
+        <v>1646.107819372302</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>1717.863541306485</v>
+        <v>1717.863541306484</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665567</v>
       </c>
       <c r="G40" s="157" t="n">
         <v>1853.25437173247</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>1575.67772535352</v>
+        <v>1575.677725353519</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>11306634.48479381</v>
+        <v>11306634.4847938</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>16037396.42810286</v>
@@ -4977,7 +4977,7 @@
         <v>1403.986729647646</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>1454.660697278588</v>
+        <v>1454.660697278586</v>
       </c>
       <c r="X40" s="157" t="n">
         <v>1514.639831400706</v>
@@ -4989,25 +4989,25 @@
         <v>1266.485950963122</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>1368.13111179333</v>
+        <v>1368.131111793329</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>11306634.48479381</v>
+        <v>11306634.4847938</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>16037396.42810286</v>
@@ -5026,13 +5026,13 @@
         <v>709.7403732238347</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>770.4360990094219</v>
+        <v>770.4360990094222</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>832.1157498394168</v>
+        <v>832.1157498394169</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>899.0376971792157</v>
+        <v>899.0376971792159</v>
       </c>
       <c r="H41" s="179" t="n">
         <v>65.27024461821777</v>
@@ -5041,10 +5041,10 @@
         <v>74.17117262775653</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>84.13364017327402</v>
+        <v>84.13364017327403</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>96.00343358786826</v>
+        <v>96.00343358786829</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>110.3183109502088</v>
@@ -5059,10 +5059,10 @@
         <v>136198539.1712981</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>157317526.8084562</v>
+        <v>157317526.8084563</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>183539890.5770544</v>
+        <v>183539890.5770545</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5076,13 +5076,13 @@
         <v>832.8009244367673</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>903.3294174729788</v>
+        <v>903.3294174729792</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>974.5102411816591</v>
+        <v>974.5102411816594</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1051.627549110226</v>
+        <v>1051.627549110227</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>77.34360466637504</v>
@@ -5091,13 +5091,13 @@
         <v>87.89461728106987</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>99.69729773514514</v>
+        <v>99.69729773514518</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>113.7547884640365</v>
+        <v>113.7547884640366</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>130.704340881594</v>
+        <v>130.7043408815941</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>102769764.677513</v>
@@ -5109,10 +5109,10 @@
         <v>136198539.1712981</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>157317526.8084562</v>
+        <v>157317526.8084563</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>183539890.5770544</v>
+        <v>183539890.5770545</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5374,7 +5374,7 @@
         <v>0.1467119925647543</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.1646855323067668</v>
+        <v>0.1646855323067667</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.1856576529803868</v>
@@ -5404,7 +5404,7 @@
         <v>18677.48044612669</v>
       </c>
       <c r="N46" s="152" t="n">
-        <v>22216.91854029268</v>
+        <v>22216.91854029267</v>
       </c>
       <c r="O46" s="152" t="n">
         <v>26511.5570277442</v>
@@ -5445,7 +5445,7 @@
         <v>0.02579856200590001</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.03042799910542656</v>
+        <v>0.03042799910542657</v>
       </c>
       <c r="AC46" s="150" t="n">
         <v>0.03588068291344702</v>
@@ -5454,7 +5454,7 @@
         <v>18677.48044612669</v>
       </c>
       <c r="AE46" s="152" t="n">
-        <v>22216.91854029268</v>
+        <v>22216.91854029267</v>
       </c>
       <c r="AF46" s="152" t="n">
         <v>26511.5570277442</v>
@@ -5578,13 +5578,13 @@
         <v>0.1329001492104268</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1492719468400522</v>
+        <v>0.1492719468400521</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.1679901594943659</v>
       </c>
       <c r="F48" s="162" t="n">
-        <v>0.187562507470907</v>
+        <v>0.1875625074709071</v>
       </c>
       <c r="G48" s="163" t="n">
         <v>0.2080078113498099</v>
@@ -5593,7 +5593,7 @@
         <v>0.01287700094083092</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.0150376218048565</v>
+        <v>0.01503762180485649</v>
       </c>
       <c r="J48" s="162" t="n">
         <v>0.01765049650588027</v>
@@ -5614,7 +5614,7 @@
         <v>27281.56975128192</v>
       </c>
       <c r="P48" s="165" t="n">
-        <v>32485.91185734345</v>
+        <v>32485.91185734346</v>
       </c>
       <c r="Q48" s="166" t="n">
         <v>38806.27638130304</v>
@@ -5628,13 +5628,13 @@
         <v>0.1576079946251641</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.1771702125871201</v>
+        <v>0.17717021258712</v>
       </c>
       <c r="V48" s="162" t="n">
         <v>0.1994581499704282</v>
       </c>
       <c r="W48" s="162" t="n">
-        <v>0.2226986543259774</v>
+        <v>0.2226986543259775</v>
       </c>
       <c r="X48" s="163" t="n">
         <v>0.2469649062484387</v>
@@ -5643,13 +5643,13 @@
         <v>0.0153041130200634</v>
       </c>
       <c r="Z48" s="162" t="n">
-        <v>0.01787586800192747</v>
+        <v>0.01787586800192746</v>
       </c>
       <c r="AA48" s="162" t="n">
         <v>0.0209855589406025</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.0247045484180368</v>
+        <v>0.02470454841803681</v>
       </c>
       <c r="AC48" s="163" t="n">
         <v>0.02908992074845245</v>
@@ -5664,7 +5664,7 @@
         <v>27281.56975128192</v>
       </c>
       <c r="AG48" s="165" t="n">
-        <v>32485.91185734345</v>
+        <v>32485.91185734346</v>
       </c>
       <c r="AH48" s="166" t="n">
         <v>38806.27638130304</v>
@@ -5683,7 +5683,7 @@
         <v>0.2004271686348618</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.2101127866742704</v>
+        <v>0.2101127866742705</v>
       </c>
       <c r="F49" s="156" t="n">
         <v>0.2186726436872586</v>
@@ -5695,13 +5695,13 @@
         <v>0.02096256863894909</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.02269470998490039</v>
+        <v>0.0226947099849004</v>
       </c>
       <c r="J49" s="156" t="n">
         <v>0.02475040745272295</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.02714843450613702</v>
+        <v>0.02714843450613703</v>
       </c>
       <c r="L49" s="157" t="n">
         <v>0.02986171123877625</v>
@@ -5730,13 +5730,13 @@
         <v>0.2513139000434558</v>
       </c>
       <c r="U49" s="156" t="n">
-        <v>0.2630683506282652</v>
+        <v>0.2630683506282653</v>
       </c>
       <c r="V49" s="156" t="n">
         <v>0.2757810960100279</v>
       </c>
       <c r="W49" s="156" t="n">
-        <v>0.287016236841274</v>
+        <v>0.2870162368412741</v>
       </c>
       <c r="X49" s="157" t="n">
         <v>0.2986382733545502</v>
@@ -5751,10 +5751,10 @@
         <v>0.02850062189577918</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.03128965287234504</v>
+        <v>0.03128965287234505</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.0344508246929659</v>
+        <v>0.03445082469296591</v>
       </c>
       <c r="AD49" s="158" t="n">
         <v>1350.759458651388</v>
@@ -5788,7 +5788,7 @@
         <v>0.1699204551168507</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1889891736798444</v>
+        <v>0.1889891736798445</v>
       </c>
       <c r="G50" s="163" t="n">
         <v>0.208900047628034</v>
@@ -5797,13 +5797,13 @@
         <v>0.01320904216821705</v>
       </c>
       <c r="I50" s="162" t="n">
-        <v>0.01535199343351229</v>
+        <v>0.01535199343351228</v>
       </c>
       <c r="J50" s="162" t="n">
         <v>0.01794214525122255</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.02103743462430134</v>
+        <v>0.02103743462430135</v>
       </c>
       <c r="L50" s="163" t="n">
         <v>0.02468179022955405</v>
@@ -5812,13 +5812,13 @@
         <v>20726.37509147294</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="O50" s="165" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="P50" s="165" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="Q50" s="166" t="n">
         <v>40839.51133852635</v>
@@ -5832,13 +5832,13 @@
         <v>0.1615332419358509</v>
       </c>
       <c r="U50" s="162" t="n">
-        <v>0.180752319846619</v>
+        <v>0.1807523198466189</v>
       </c>
       <c r="V50" s="162" t="n">
         <v>0.2026359184822088</v>
       </c>
       <c r="W50" s="162" t="n">
-        <v>0.2253785245881947</v>
+        <v>0.2253785245881948</v>
       </c>
       <c r="X50" s="163" t="n">
         <v>0.2491108631383457</v>
@@ -5862,13 +5862,13 @@
         <v>20726.37509147294</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="AF50" s="165" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="AG50" s="165" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="AH50" s="166" t="n">
         <v>40839.51133852635</v>
@@ -5992,7 +5992,7 @@
         <v>0.1635940860104685</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1814595516902329</v>
+        <v>0.181459551690233</v>
       </c>
       <c r="G52" s="181" t="n">
         <v>0.2000451243175327</v>
@@ -6007,7 +6007,7 @@
         <v>0.01786490272791862</v>
       </c>
       <c r="K52" s="180" t="n">
-        <v>0.02093547685275697</v>
+        <v>0.02093547685275698</v>
       </c>
       <c r="L52" s="181" t="n">
         <v>0.02454695759452181</v>
@@ -6016,13 +6016,13 @@
         <v>20726.37509147294</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="O52" s="183" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="P52" s="183" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="Q52" s="184" t="n">
         <v>40839.51133852635</v>
@@ -6036,7 +6036,7 @@
         <v>0.1539157383167547</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.1717125094532997</v>
+        <v>0.1717125094532996</v>
       </c>
       <c r="V52" s="186" t="n">
         <v>0.1918125988746715</v>
@@ -6051,28 +6051,28 @@
         <v>0.01559848430394089</v>
       </c>
       <c r="Z52" s="186" t="n">
-        <v>0.01812270478803463</v>
+        <v>0.01812270478803462</v>
       </c>
       <c r="AA52" s="186" t="n">
         <v>0.02116968340614471</v>
       </c>
       <c r="AB52" s="186" t="n">
-        <v>0.02480651630651728</v>
+        <v>0.02480651630651729</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.02908305869991512</v>
+        <v>0.02908305869991513</v>
       </c>
       <c r="AD52" s="188" t="n">
         <v>20726.37509147294</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>24432.56557867787</v>
+        <v>24432.56557867786</v>
       </c>
       <c r="AF52" s="189" t="n">
         <v>28920.34207682813</v>
       </c>
       <c r="AG52" s="189" t="n">
-        <v>34306.24632833554</v>
+        <v>34306.24632833555</v>
       </c>
       <c r="AH52" s="190" t="n">
         <v>40839.51133852635</v>
@@ -6334,28 +6334,28 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.008316737834552888</v>
+        <v>0.00831673783455289</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.00775530712793584</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007241775337046654</v>
+        <v>0.007241775337046653</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002666134706614924</v>
+        <v>0.0002666134706614923</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.0008574287566231654</v>
+        <v>0.0008574287566231656</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.0008340343562962086</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008128878341321738</v>
+        <v>0.0008128878341321736</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>3.151127830097264e-05</v>
@@ -6384,16 +6384,16 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01011285538328333</v>
+        <v>0.01011285538328334</v>
       </c>
       <c r="U57" s="149" t="n">
         <v>0.009430175748948316</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008805739480871573</v>
+        <v>0.008805739480871572</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003241924328590883</v>
+        <v>0.0003241924328590882</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0.001006300505615744</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>3.900412879116093e-05</v>
+        <v>3.900412879116092e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6538,13 +6538,13 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.007262324401554549</v>
+        <v>0.00726232440155455</v>
       </c>
       <c r="D59" s="162" t="n">
         <v>0.006805013685711213</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.00636769001075895</v>
+        <v>0.006367690010758948</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.000234444495243558</v>
@@ -6553,13 +6553,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.0007036633044208829</v>
+        <v>0.000703663304420883</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0.0006855355232436792</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006690444882231272</v>
+        <v>0.0006690444882231271</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>2.59682824170971e-05</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.008612483823732281</v>
+        <v>0.008612483823732283</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.00807684060453496</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.00756048850095742</v>
+        <v>0.007560488500957419</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002783630604478445</v>
@@ -6603,13 +6603,13 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0008362927663367534</v>
+        <v>0.0008362927663367536</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.0008149255702240501</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0007954604867242205</v>
+        <v>0.0007954604867242204</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>3.087954763552655e-05</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.006927129957544079</v>
+        <v>0.006927129957544081</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0.006492570992111518</v>
@@ -6751,22 +6751,22 @@
         <v>0.006075886650521905</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002236932070810983</v>
+        <v>0.0002236932070810982</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0006747667277066882</v>
+        <v>0.0006747667277066883</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.0006573899783738695</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006415616103350308</v>
+        <v>0.0006415616103350306</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.490053333870305e-05</v>
+        <v>2.490053333870304e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008251715430144569</v>
+        <v>0.008251715430144571</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.00774002178607045</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.00724570135582342</v>
+        <v>0.007245701355823418</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002667647251463497</v>
@@ -6807,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.0008008547206182185</v>
+        <v>0.0008008547206182186</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.0007804110733172412</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007617676189276554</v>
+        <v>0.0007617676189276553</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>2.957126317615418e-05</v>
@@ -6946,28 +6946,28 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.00669963882986987</v>
+        <v>0.006699638829869871</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0.006266406302521571</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005849673146248341</v>
+        <v>0.00584967314624834</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.000214780922540303</v>
+        <v>0.0002147809225403029</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006724431358601231</v>
+        <v>0.0006724431358601232</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0.0006548686268315282</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006387996308201322</v>
+        <v>0.0006387996308201321</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>2.477985308776847e-05</v>
@@ -6996,13 +6996,13 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.007862585171879582</v>
+        <v>0.007862585171879584</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.007352926729998082</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006858689309083399</v>
+        <v>0.006858689309083398</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.0002515349681415862</v>
@@ -7011,16 +7011,16 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0007968282693714074</v>
+        <v>0.0007968282693714075</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0.0007760350185322119</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007569694697128567</v>
+        <v>0.0007569694697128566</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>2.936173052174266e-05</v>
+        <v>2.936173052174265e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
@@ -7297,46 +7297,46 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003529972139729033</v>
+        <v>0.003529972139729034</v>
       </c>
       <c r="D68" s="149" t="n">
         <v>0.005198304241285984</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.006936362289539943</v>
+        <v>0.006936362289539941</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.008578382940314789</v>
+        <v>0.008578382940314785</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.01018237916068306</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.0003639287041257321</v>
+        <v>0.0003639287041257322</v>
       </c>
       <c r="I68" s="149" t="n">
         <v>0.0005590448270056797</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0007786052805940402</v>
+        <v>0.00077860528059404</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.001013886550945446</v>
+        <v>0.001013886550945445</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.001275543549729376</v>
+        <v>0.001275543549729377</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>449.3905676188062</v>
+        <v>449.3905676188064</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>701.2777641036489</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>990.4992412225498</v>
+        <v>990.4992412225496</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1306.509020116175</v>
+        <v>1306.509020116174</v>
       </c>
       <c r="Q68" s="153" t="n">
         <v>1670.077092442816</v>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004292319713119596</v>
+        <v>0.004292319713119597</v>
       </c>
       <c r="U68" s="149" t="n">
         <v>0.006320951805409377</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008434368151986917</v>
+        <v>0.008434368151986915</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.01043100646234235</v>
@@ -7362,31 +7362,31 @@
         <v>0.01238140842698351</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.000450603212970459</v>
+        <v>0.0004506032129704591</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.0006921262117086392</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009638610084173972</v>
+        <v>0.000963861008417397</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.001254971671888077</v>
+        <v>0.001254971671888076</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>0.001578618898823262</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>449.3905676188062</v>
+        <v>449.3905676188064</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>701.2777641036489</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>990.4992412225498</v>
+        <v>990.4992412225496</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1306.509020116175</v>
+        <v>1306.509020116174</v>
       </c>
       <c r="AH68" s="153" t="n">
         <v>1670.077092442816</v>
@@ -7507,40 +7507,40 @@
         <v>0.004561332120170602</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006099140446425592</v>
+        <v>0.00609914044642559</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.00754333475145945</v>
+        <v>0.007543334751459446</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008951878746909538</v>
+        <v>0.008951878746909539</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.0002986642010086786</v>
+        <v>0.0002986642010086787</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.0004595075551802577</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006408283524614336</v>
+        <v>0.0006408283524614335</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008355386932378166</v>
+        <v>0.0008355386932378161</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.001052644996048486</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>449.3905676188062</v>
+        <v>449.3905676188064</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>701.2777641036489</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>990.4992412225498</v>
+        <v>990.4992412225496</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1306.509020116175</v>
+        <v>1306.509020116174</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>1670.077092442816</v>
@@ -7551,46 +7551,46 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003655499133967392</v>
+        <v>0.003655499133967393</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.005413824891538492</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007241634114256916</v>
+        <v>0.007241634114256914</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008956430157242221</v>
+        <v>0.008956430157242215</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01062844650463616</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.0003549577039161735</v>
+        <v>0.0003549577039161736</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.0005462364002024506</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007619129103200216</v>
+        <v>0.0007619129103200215</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.0009935603928188858</v>
+        <v>0.0009935603928188854</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.001251921462023461</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>449.3905676188062</v>
+        <v>449.3905676188064</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>701.2777641036489</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>990.4992412225498</v>
+        <v>990.4992412225496</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1306.509020116175</v>
+        <v>1306.509020116174</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>1670.077092442816</v>
@@ -7606,7 +7606,7 @@
         <v>0.01071881309347009</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01616070982960535</v>
+        <v>0.01616070982960536</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.02198198684610884</v>
@@ -7615,13 +7615,13 @@
         <v>0.02773434376901519</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03359134568995958</v>
+        <v>0.0335913456899596</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.001173509734148188</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.0018299047241504</v>
+        <v>0.001829904724150401</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.00258938610863807</v>
@@ -7630,22 +7630,22 @@
         <v>0.003443247416264123</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004408680622085193</v>
+        <v>0.004408680622085196</v>
       </c>
       <c r="M71" s="158" t="n">
         <v>75.61713454690479</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>119.5673136624068</v>
+        <v>119.5673136624069</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>171.4482601183611</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>230.8737898888108</v>
+        <v>230.8737898888109</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>300.1798351199909</v>
+        <v>300.179835119991</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>0.01406885354115292</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.02121155185104381</v>
+        <v>0.02121155185104382</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>0.02885220133839797</v>
@@ -7665,37 +7665,37 @@
         <v>0.03640239055795891</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04408993035340669</v>
+        <v>0.04408993035340671</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.001349760907245852</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.002105837796603932</v>
+        <v>0.002105837796603933</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>0.002981733313499755</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003968479890954622</v>
+        <v>0.003968479890954623</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.005086201591873578</v>
+        <v>0.005086201591873581</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>75.61713454690479</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>119.5673136624068</v>
+        <v>119.5673136624069</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>171.4482601183611</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>230.8737898888108</v>
+        <v>230.8737898888109</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>300.1798351199909</v>
+        <v>300.179835119991</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7711,31 +7711,31 @@
         <v>0.005093901337955694</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006826981773771238</v>
+        <v>0.006826981773771237</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008469265454217251</v>
+        <v>0.008469265454217246</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.01007815109724538</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003345905323984361</v>
+        <v>0.0003345905323984362</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.0005157709780094771</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007208708246939324</v>
+        <v>0.0007208708246939322</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009427609785245127</v>
+        <v>0.0009427609785245122</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>0.001190745593925748</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>525.0077021657111</v>
+        <v>525.0077021657112</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>820.8450777660557</v>
@@ -7744,7 +7744,7 @@
         <v>1161.947501340911</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1537.382810004986</v>
+        <v>1537.382810004985</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>1970.256927562807</v>
@@ -7755,13 +7755,13 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004091704207698585</v>
+        <v>0.004091704207698586</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.006072618594355646</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.008141407820724731</v>
+        <v>0.008141407820724729</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.01009999946161372</v>
@@ -7770,13 +7770,13 @@
         <v>0.01201807729189118</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0003971126558894711</v>
+        <v>0.0003971126558894712</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.0006122901105519177</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.000855936581671006</v>
+        <v>0.0008559365816710059</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001119599834627842</v>
@@ -7785,7 +7785,7 @@
         <v>0.001414368373020928</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>525.0077021657111</v>
+        <v>525.0077021657112</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>820.8450777660557</v>
@@ -7794,7 +7794,7 @@
         <v>1161.947501340911</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1537.382810004986</v>
+        <v>1537.382810004985</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>1970.256927562807</v>
@@ -7909,37 +7909,37 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003322089888133612</v>
+        <v>0.003322089888133613</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.004916458439556845</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006572803978909991</v>
+        <v>0.00657280397890999</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.008131836774265662</v>
+        <v>0.008131836774265658</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.009650955143529486</v>
+        <v>0.009650955143529488</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.0003334383537252801</v>
+        <v>0.0003334383537252802</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.0005137927915544359</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007177674119918337</v>
+        <v>0.0007177674119918336</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009381918944044217</v>
+        <v>0.0009381918944044213</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.001184240742997641</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>525.0077021657111</v>
+        <v>525.0077021657112</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>820.8450777660557</v>
@@ -7948,7 +7948,7 @@
         <v>1161.947501340911</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1537.382810004986</v>
+        <v>1537.382810004985</v>
       </c>
       <c r="Q74" s="184" t="n">
         <v>1970.256927562807</v>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003898749672539852</v>
+        <v>0.003898749672539853</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.005768913940769442</v>
@@ -7968,13 +7968,13 @@
         <v>0.007706553725957003</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.009523384478263763</v>
+        <v>0.00952338447826376</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.01128897079177703</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0003951160955805098</v>
+        <v>0.0003951160955805099</v>
       </c>
       <c r="Z74" s="186" t="n">
         <v>0.0006088567724564988</v>
@@ -7986,10 +7986,10 @@
         <v>0.001111666702930666</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.001403079909630749</v>
+        <v>0.00140307990963075</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>525.0077021657111</v>
+        <v>525.0077021657112</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>820.8450777660557</v>
@@ -7998,7 +7998,7 @@
         <v>1161.947501340911</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1537.382810004986</v>
+        <v>1537.382810004985</v>
       </c>
       <c r="AH74" s="190" t="n">
         <v>1970.256927562807</v>
@@ -8263,43 +8263,43 @@
         <v>437.1406345268638</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>483.5850484376496</v>
+        <v>483.5850484376497</v>
       </c>
       <c r="E79" s="149" t="n">
         <v>527.3047029857898</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>571.6926319374734</v>
+        <v>571.6926319374736</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>620.1946372292489</v>
+        <v>620.194637229249</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>45.06778477188595</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>52.00652120343759</v>
+        <v>52.0065212034376</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>59.18984751502052</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>67.56885007685833</v>
+        <v>67.56885007685835</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>77.69159413637969</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>55651112.84259372</v>
+        <v>55651112.84259373</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>65238090.30431327</v>
+        <v>65238090.30431328</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>75298100.99281134</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>87070207.23568405</v>
+        <v>87070207.2356841</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>101722086.7684688</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>531.5473575180391</v>
+        <v>531.5473575180392</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>588.0221016526643</v>
@@ -8319,13 +8319,13 @@
         <v>641.1836359763219</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>695.1577680436898</v>
+        <v>695.1577680436901</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>754.134469614966</v>
+        <v>754.1344696149661</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>55.80128302453692</v>
+        <v>55.80128302453693</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>64.38674461487251</v>
@@ -8334,22 +8334,22 @@
         <v>73.27305315778555</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>83.63558296481672</v>
+        <v>83.63558296481676</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>96.15149463882776</v>
+        <v>96.15149463882777</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>55651112.84259372</v>
+        <v>55651112.84259373</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>65238090.30431327</v>
+        <v>65238090.30431328</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>75298100.99281134</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>87070207.23568405</v>
+        <v>87070207.2356841</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>101722086.7684688</v>
@@ -8415,7 +8415,7 @@
         <v>1531.065819031179</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1686.338540130558</v>
+        <v>1686.338540130557</v>
       </c>
       <c r="V80" s="156" t="n">
         <v>1828.508765780161</v>
@@ -8430,7 +8430,7 @@
         <v>103.9150640677695</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>115.8422823421933</v>
+        <v>115.8422823421932</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>129.846875905146</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>573.2619537573747</v>
+        <v>573.2619537573748</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>628.2294324190809</v>
@@ -8473,13 +8473,13 @@
         <v>681.4398912224008</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>735.6266822511176</v>
+        <v>735.6266822511179</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>794.5649321070103</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>55.54466839753658</v>
+        <v>55.54466839753659</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>63.28768942446047</v>
@@ -8488,13 +8488,13 @@
         <v>71.59795820892597</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>81.48180838455443</v>
+        <v>81.48180838455445</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>93.43232001514751</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>83576304.0065254</v>
+        <v>83576304.00652541</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>96586549.74119264</v>
@@ -8503,7 +8503,7 @@
         <v>110665707.9179295</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>127410876.9484571</v>
+        <v>127410876.9484572</v>
       </c>
       <c r="Q81" s="166" t="n">
         <v>148235329.039551</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>679.8387169870449</v>
+        <v>679.838716987045</v>
       </c>
       <c r="U81" s="162" t="n">
         <v>745.642730944203</v>
@@ -8523,13 +8523,13 @@
         <v>809.0875110088125</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>873.4318730997878</v>
+        <v>873.4318730997882</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>943.3763698234507</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>66.01396448783602</v>
+        <v>66.01396448783603</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>75.2327992404536</v>
@@ -8538,13 +8538,13 @@
         <v>85.12639695544227</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>96.89209871589817</v>
+        <v>96.8920987158982</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>111.1200139768864</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>83576304.0065254</v>
+        <v>83576304.00652541</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>96586549.74119264</v>
@@ -8553,7 +8553,7 @@
         <v>110665707.9179295</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>127410876.9484571</v>
+        <v>127410876.9484572</v>
       </c>
       <c r="AH81" s="166" t="n">
         <v>148235329.039551</v>
@@ -8572,7 +8572,7 @@
         <v>1670.947839770544</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1827.980466776747</v>
+        <v>1827.980466776746</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>1986.430386873107</v>
@@ -8602,7 +8602,7 @@
         <v>12362745.60820109</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>14257313.16979204</v>
+        <v>14257313.16979203</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>16535985.69294635</v>
@@ -8619,7 +8619,7 @@
         <v>1985.660672735431</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>2193.183165677078</v>
+        <v>2193.183165677079</v>
       </c>
       <c r="V82" s="156" t="n">
         <v>2399.294515065067</v>
@@ -8637,7 +8637,7 @@
         <v>217.7345645236693</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>247.9553050583274</v>
+        <v>247.9553050583273</v>
       </c>
       <c r="AB82" s="156" t="n">
         <v>284.2363645140271</v>
@@ -8652,7 +8652,7 @@
         <v>12362745.60820109</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>14257313.16979204</v>
+        <v>14257313.16979203</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>16535985.69294635</v>
@@ -8668,22 +8668,22 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>616.6284233106685</v>
+        <v>616.6284233106686</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>676.1043909284153</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>733.980827108034</v>
+        <v>733.9808271080338</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>792.9867454468549</v>
+        <v>792.9867454468551</v>
       </c>
       <c r="G83" s="163" t="n">
         <v>857.0186278194375</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>60.06532950275268</v>
+        <v>60.06532950275269</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>68.45735710413237</v>
@@ -8692,13 +8692,13 @@
         <v>77.50209121396615</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>88.27175911958003</v>
+        <v>88.27175911958004</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>101.2577748776968</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>94248813.30627236</v>
+        <v>94248813.30627237</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>108949295.3493937</v>
@@ -8718,28 +8718,28 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>734.5383017907646</v>
+        <v>734.5383017907648</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>806.0077774739783</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>875.2970850218633</v>
+        <v>875.2970850218632</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>945.6741845412233</v>
+        <v>945.6741845412236</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>1021.984688495066</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>71.28923330475507</v>
+        <v>71.28923330475509</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>81.26816850212755</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>92.02324848450074</v>
+        <v>92.02324848450073</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>104.829377927017</v>
@@ -8748,7 +8748,7 @@
         <v>120.2740493351916</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>94248813.30627236</v>
+        <v>94248813.30627237</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>108949295.3493937</v>
@@ -8770,46 +8770,46 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>1646.107819372303</v>
+        <v>1646.107819372302</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>1717.863541306485</v>
+        <v>1717.863541306484</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665567</v>
       </c>
       <c r="G84" s="157" t="n">
         <v>1853.25437173247</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>1575.67772535352</v>
+        <v>1575.677725353519</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>11306634.48479381</v>
+        <v>11306634.4847938</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>16037396.42810286</v>
@@ -8829,7 +8829,7 @@
         <v>1403.986729647646</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>1454.660697278588</v>
+        <v>1454.660697278586</v>
       </c>
       <c r="X84" s="157" t="n">
         <v>1514.639831400706</v>
@@ -8841,25 +8841,25 @@
         <v>1266.485950963122</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>1368.13111179333</v>
+        <v>1368.131111793329</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>11306634.48479381</v>
+        <v>11306634.4847938</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>16037396.42810286</v>
@@ -8875,10 +8875,10 @@
         <v>650.4371478708844</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>709.8978951438908</v>
+        <v>709.8978951438907</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>770.6121155725576</v>
+        <v>770.6121155725574</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>832.3055560088039</v>
@@ -8893,7 +8893,7 @@
         <v>74.18763440161908</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>84.15286164304474</v>
+        <v>84.15286164304473</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>96.02533203646851</v>
@@ -8908,7 +8908,7 @@
         <v>118523567.3420786</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>136229655.5725154</v>
+        <v>136229655.5725153</v>
       </c>
       <c r="P85" s="183" t="n">
         <v>157353411.0434881</v>
@@ -8925,7 +8925,7 @@
         <v>763.3422642558473</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>832.9857587868914</v>
+        <v>832.9857587868913</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>903.5357953148886</v>
@@ -8940,7 +8940,7 @@
         <v>77.36039509504394</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>87.9141248776489</v>
+        <v>87.91412487764889</v>
       </c>
       <c r="AA85" s="186" t="n">
         <v>99.72007493331098</v>
@@ -8958,7 +8958,7 @@
         <v>118523567.3420786</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>136229655.5725154</v>
+        <v>136229655.5725153</v>
       </c>
       <c r="AG85" s="189" t="n">
         <v>157353411.0434881</v>
@@ -9874,7 +9874,7 @@
         <v>5815.89985498167</v>
       </c>
       <c r="E95" s="80" t="n">
-        <v>6581.800133085534</v>
+        <v>6581.800133085533</v>
       </c>
       <c r="F95" s="80" t="n">
         <v>7532.334804665247</v>
@@ -9924,7 +9924,7 @@
         <v>7116.108799169399</v>
       </c>
       <c r="V95" s="80" t="n">
-        <v>8053.234582659765</v>
+        <v>8053.234582659764</v>
       </c>
       <c r="W95" s="80" t="n">
         <v>9216.271826939363</v>
@@ -9954,7 +9954,7 @@
         <v>7559.714330351571</v>
       </c>
       <c r="AF95" s="80" t="n">
-        <v>8604.790564518178</v>
+        <v>8604.790564518176</v>
       </c>
       <c r="AG95" s="80" t="n">
         <v>9799.169309519959</v>
@@ -10065,7 +10065,7 @@
         <v>1221520.607621158</v>
       </c>
       <c r="AC96" s="137" t="n">
-        <v>1229707.778647045</v>
+        <v>1229707.778647044</v>
       </c>
       <c r="AD96" s="135" t="n">
         <v>1328742.888579021</v>
